--- a/analysis/scenario_comparison.xlsx
+++ b/analysis/scenario_comparison.xlsx
@@ -1191,12 +1191,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Gross cost [M€]</t>
+          <t>Gross cost [Bn€]</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Net cost [M€]</t>
+          <t>Net cost [Bn€]</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
